--- a/netdoc/H3C-VLAN配置整理_v3.xlsx
+++ b/netdoc/H3C-VLAN配置整理_v3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15280" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN概览" sheetId="1" r:id="rId1"/>
@@ -543,7 +543,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -581,13 +581,6 @@
       <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1082,28 +1075,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1112,118 +1108,115 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1604,7 +1597,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1615,12 +1608,12 @@
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" spans="1:8">
+    <row r="1" ht="21" spans="1:8">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="33" spans="1:8">
+    <row r="3" ht="15" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1932,7 +1925,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" ht="28" spans="1:8">
+    <row r="15" ht="27" spans="1:8">
       <c r="A15" s="3" t="s">
         <v>42</v>
       </c>
@@ -1984,12 +1977,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:8">
+    <row r="18" ht="18" spans="1:8">
       <c r="A18" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" ht="33" spans="1:8">
+    <row r="19" ht="30" spans="1:8">
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
@@ -2029,7 +2022,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -2038,21 +2031,21 @@
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="34.6090909090909" customWidth="1"/>
-    <col min="10" max="10" width="48.0363636363636" customWidth="1"/>
+    <col min="9" max="9" width="34.6083333333333" customWidth="1"/>
+    <col min="10" max="10" width="48.0333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:10">
+    <row r="1" ht="19.5" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" ht="14.5" spans="1:10">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
+    <row r="3" ht="15" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -3513,7 +3506,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -3524,17 +3517,17 @@
     <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:8">
+    <row r="1" ht="19.5" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="2" ht="14.5" spans="1:8">
+    <row r="2" ht="16.5" spans="1:8">
       <c r="A2" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:8">
+    <row r="3" ht="15" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -4929,7 +4922,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -4940,17 +4933,17 @@
     <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:8">
+    <row r="1" ht="19.5" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="2" ht="14.5" spans="1:8">
+    <row r="2" ht="16.5" spans="1:8">
       <c r="A2" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:8">
+    <row r="3" ht="15" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -6351,7 +6344,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -6359,12 +6352,12 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:6">
+    <row r="1" ht="19.5" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="3" ht="33" spans="1:6">
+    <row r="3" ht="15" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
